--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ13"/>
+  <dimension ref="A1:FQ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ASFGF</t>
+          <t>RGSDG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASFCdE</t>
+          <t>DZSVBZDV</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RH | Side | ASDVAv | RH | ASVzsVasdv</t>
+          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RGSDG</t>
+          <t>SAvfas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DZSVBZDV</t>
+          <t>AFsDFFWAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
+          <t>RH | Side | SFCc | RH | DVZDGV</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAvfas</t>
+          <t>VCNBVBN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AFsDFFWAS</t>
+          <t>VFBFCXB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>RH | Side | SFCc | RH | DVZDGV</t>
+          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>CVDZV</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>ZCVDV</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | SDVd | RH | ZXVV</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CVDZV</t>
+          <t>VsgsdVDsvB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ZCVDV</t>
+          <t>DVasdvsdv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VsgsdVDsvB</t>
+          <t>DASGVSDEGV</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DASGVSDEGV</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DVasdvsdv</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>RH | Side | SDVd | RH | ZXVV</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -4510,279 +4510,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
-      <c r="BW13" t="inlineStr"/>
-      <c r="BX13" t="inlineStr"/>
-      <c r="BY13" t="inlineStr"/>
-      <c r="BZ13" t="inlineStr"/>
-      <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="inlineStr"/>
-      <c r="CC13" t="inlineStr"/>
-      <c r="CD13" t="inlineStr"/>
-      <c r="CE13" t="inlineStr"/>
-      <c r="CF13" t="inlineStr"/>
-      <c r="CG13" t="inlineStr"/>
-      <c r="CH13" t="inlineStr"/>
-      <c r="CI13" t="inlineStr"/>
-      <c r="CJ13" t="inlineStr"/>
-      <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
-      <c r="DJ13" t="inlineStr"/>
-      <c r="DK13" t="inlineStr"/>
-      <c r="DL13" t="inlineStr"/>
-      <c r="DM13" t="inlineStr"/>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr"/>
-      <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
-      <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
-      <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="inlineStr"/>
-      <c r="DV13" t="inlineStr"/>
-      <c r="DW13" t="inlineStr"/>
-      <c r="DX13" t="inlineStr"/>
-      <c r="DY13" t="inlineStr"/>
-      <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
-      <c r="ED13" t="inlineStr"/>
-      <c r="EE13" t="inlineStr"/>
-      <c r="EF13" t="inlineStr"/>
-      <c r="EG13" t="inlineStr"/>
-      <c r="EH13" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI13" t="inlineStr"/>
-      <c r="EJ13" t="inlineStr"/>
-      <c r="EK13" t="inlineStr"/>
-      <c r="EL13" t="inlineStr"/>
-      <c r="EM13" t="inlineStr"/>
-      <c r="EN13" t="inlineStr"/>
-      <c r="EO13" t="inlineStr"/>
-      <c r="EP13" t="inlineStr"/>
-      <c r="EQ13" t="inlineStr"/>
-      <c r="ER13" t="inlineStr"/>
-      <c r="ES13" t="inlineStr"/>
-      <c r="ET13" t="inlineStr"/>
-      <c r="EU13" t="inlineStr"/>
-      <c r="EV13" t="inlineStr"/>
-      <c r="EW13" t="inlineStr"/>
-      <c r="EX13" t="inlineStr"/>
-      <c r="EY13" t="inlineStr"/>
-      <c r="EZ13" t="inlineStr"/>
-      <c r="FA13" t="inlineStr"/>
-      <c r="FB13" t="inlineStr"/>
-      <c r="FC13" t="inlineStr"/>
-      <c r="FD13" t="inlineStr"/>
-      <c r="FE13" t="inlineStr"/>
-      <c r="FF13" t="inlineStr"/>
-      <c r="FG13" t="inlineStr"/>
-      <c r="FH13" t="inlineStr"/>
-      <c r="FI13" t="inlineStr"/>
-      <c r="FJ13" t="inlineStr"/>
-      <c r="FK13" t="inlineStr"/>
-      <c r="FL13" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ12"/>
+  <dimension ref="A1:FQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DASGVSDEGV</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DVasdvsdv</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>RH | Side | SDVd | RH | ZXVV</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4217,299 +4217,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr"/>
-      <c r="BX12" t="inlineStr"/>
-      <c r="BY12" t="inlineStr"/>
-      <c r="BZ12" t="inlineStr"/>
-      <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
-      <c r="CC12" t="inlineStr"/>
-      <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr"/>
-      <c r="CF12" t="inlineStr"/>
-      <c r="CG12" t="inlineStr"/>
-      <c r="CH12" t="inlineStr"/>
-      <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
-      <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="inlineStr"/>
-      <c r="DC12" t="inlineStr"/>
-      <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="inlineStr"/>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
-      <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
-      <c r="DJ12" t="inlineStr"/>
-      <c r="DK12" t="inlineStr"/>
-      <c r="DL12" t="inlineStr"/>
-      <c r="DM12" t="inlineStr"/>
-      <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
-      <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
-      <c r="DT12" t="inlineStr"/>
-      <c r="DU12" t="inlineStr"/>
-      <c r="DV12" t="inlineStr"/>
-      <c r="DW12" t="inlineStr"/>
-      <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
-      <c r="DZ12" t="inlineStr"/>
-      <c r="EA12" t="inlineStr"/>
-      <c r="EB12" t="inlineStr"/>
-      <c r="EC12" t="inlineStr"/>
-      <c r="ED12" t="inlineStr"/>
-      <c r="EE12" t="inlineStr"/>
-      <c r="EF12" t="inlineStr"/>
-      <c r="EG12" t="inlineStr"/>
-      <c r="EH12" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI12" t="inlineStr"/>
-      <c r="EJ12" t="inlineStr"/>
-      <c r="EK12" t="inlineStr"/>
-      <c r="EL12" t="inlineStr"/>
-      <c r="EM12" t="inlineStr"/>
-      <c r="EN12" t="inlineStr"/>
-      <c r="EO12" t="inlineStr"/>
-      <c r="EP12" t="inlineStr"/>
-      <c r="EQ12" t="inlineStr"/>
-      <c r="ER12" t="inlineStr"/>
-      <c r="ES12" t="inlineStr"/>
-      <c r="ET12" t="inlineStr"/>
-      <c r="EU12" t="inlineStr"/>
-      <c r="EV12" t="inlineStr"/>
-      <c r="EW12" t="inlineStr"/>
-      <c r="EX12" t="inlineStr"/>
-      <c r="EY12" t="inlineStr"/>
-      <c r="EZ12" t="inlineStr"/>
-      <c r="FA12" t="inlineStr"/>
-      <c r="FB12" t="inlineStr"/>
-      <c r="FC12" t="inlineStr"/>
-      <c r="FD12" t="inlineStr"/>
-      <c r="FE12" t="inlineStr"/>
-      <c r="FF12" t="inlineStr"/>
-      <c r="FG12" t="inlineStr"/>
-      <c r="FH12" t="inlineStr"/>
-      <c r="FI12" t="inlineStr"/>
-      <c r="FJ12" t="inlineStr"/>
-      <c r="FK12" t="inlineStr"/>
-      <c r="FL12" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ11"/>
+  <dimension ref="A1:FQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VsgsdVDsvB</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DVasdvsdv</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>RH | Side | SDVd | RH | ZXVV</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3924,299 +3924,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr"/>
-      <c r="BX11" t="inlineStr"/>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
-      <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
-      <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
-      <c r="CE11" t="inlineStr"/>
-      <c r="CF11" t="inlineStr"/>
-      <c r="CG11" t="inlineStr"/>
-      <c r="CH11" t="inlineStr"/>
-      <c r="CI11" t="inlineStr"/>
-      <c r="CJ11" t="inlineStr"/>
-      <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
-      <c r="DJ11" t="inlineStr"/>
-      <c r="DK11" t="inlineStr"/>
-      <c r="DL11" t="inlineStr"/>
-      <c r="DM11" t="inlineStr"/>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr"/>
-      <c r="DP11" t="inlineStr"/>
-      <c r="DQ11" t="inlineStr"/>
-      <c r="DR11" t="inlineStr"/>
-      <c r="DS11" t="inlineStr"/>
-      <c r="DT11" t="inlineStr"/>
-      <c r="DU11" t="inlineStr"/>
-      <c r="DV11" t="inlineStr"/>
-      <c r="DW11" t="inlineStr"/>
-      <c r="DX11" t="inlineStr"/>
-      <c r="DY11" t="inlineStr"/>
-      <c r="DZ11" t="inlineStr"/>
-      <c r="EA11" t="inlineStr"/>
-      <c r="EB11" t="inlineStr"/>
-      <c r="EC11" t="inlineStr"/>
-      <c r="ED11" t="inlineStr"/>
-      <c r="EE11" t="inlineStr"/>
-      <c r="EF11" t="inlineStr"/>
-      <c r="EG11" t="inlineStr"/>
-      <c r="EH11" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI11" t="inlineStr"/>
-      <c r="EJ11" t="inlineStr"/>
-      <c r="EK11" t="inlineStr"/>
-      <c r="EL11" t="inlineStr"/>
-      <c r="EM11" t="inlineStr"/>
-      <c r="EN11" t="inlineStr"/>
-      <c r="EO11" t="inlineStr"/>
-      <c r="EP11" t="inlineStr"/>
-      <c r="EQ11" t="inlineStr"/>
-      <c r="ER11" t="inlineStr"/>
-      <c r="ES11" t="inlineStr"/>
-      <c r="ET11" t="inlineStr"/>
-      <c r="EU11" t="inlineStr"/>
-      <c r="EV11" t="inlineStr"/>
-      <c r="EW11" t="inlineStr"/>
-      <c r="EX11" t="inlineStr"/>
-      <c r="EY11" t="inlineStr"/>
-      <c r="EZ11" t="inlineStr"/>
-      <c r="FA11" t="inlineStr"/>
-      <c r="FB11" t="inlineStr"/>
-      <c r="FC11" t="inlineStr"/>
-      <c r="FD11" t="inlineStr"/>
-      <c r="FE11" t="inlineStr"/>
-      <c r="FF11" t="inlineStr"/>
-      <c r="FG11" t="inlineStr"/>
-      <c r="FH11" t="inlineStr"/>
-      <c r="FI11" t="inlineStr"/>
-      <c r="FJ11" t="inlineStr"/>
-      <c r="FK11" t="inlineStr"/>
-      <c r="FL11" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ10"/>
+  <dimension ref="A1:FQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AcvasV</t>
+          <t>EFGeq</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SAVVSV</t>
+          <t>EGWEGWE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RH | Side | ASVs | RH | ASVVAVS</t>
+          <t>RH | Side | WEGWEG | RH | GSDEGAG</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EFGeq</t>
+          <t>RGSDG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EGWEGWE</t>
+          <t>DZSVBZDV</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RH | Side | WEGWEG | RH | GSDEGAG</t>
+          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RGSDG</t>
+          <t>SAvfas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DZSVBZDV</t>
+          <t>AFsDFFWAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
+          <t>RH | Side | SFCc | RH | DVZDGV</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAvfas</t>
+          <t>VCNBVBN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AFsDFFWAS</t>
+          <t>VFBFCXB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RH | Side | SFCc | RH | DVZDGV</t>
+          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>CVDZV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>ZCVDV</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | SDVd | RH | ZXVV</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CVDZV</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZCVDV</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>RH | Side | SDVd | RH | ZXVV</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3631,299 +3631,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
-      <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
-      <c r="CE10" t="inlineStr"/>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
-      <c r="CI10" t="inlineStr"/>
-      <c r="CJ10" t="inlineStr"/>
-      <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
-      <c r="DT10" t="inlineStr"/>
-      <c r="DU10" t="inlineStr"/>
-      <c r="DV10" t="inlineStr"/>
-      <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr"/>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr"/>
-      <c r="EB10" t="inlineStr"/>
-      <c r="EC10" t="inlineStr"/>
-      <c r="ED10" t="inlineStr"/>
-      <c r="EE10" t="inlineStr"/>
-      <c r="EF10" t="inlineStr"/>
-      <c r="EG10" t="inlineStr"/>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr"/>
-      <c r="EJ10" t="inlineStr"/>
-      <c r="EK10" t="inlineStr"/>
-      <c r="EL10" t="inlineStr"/>
-      <c r="EM10" t="inlineStr"/>
-      <c r="EN10" t="inlineStr"/>
-      <c r="EO10" t="inlineStr"/>
-      <c r="EP10" t="inlineStr"/>
-      <c r="EQ10" t="inlineStr"/>
-      <c r="ER10" t="inlineStr"/>
-      <c r="ES10" t="inlineStr"/>
-      <c r="ET10" t="inlineStr"/>
-      <c r="EU10" t="inlineStr"/>
-      <c r="EV10" t="inlineStr"/>
-      <c r="EW10" t="inlineStr"/>
-      <c r="EX10" t="inlineStr"/>
-      <c r="EY10" t="inlineStr"/>
-      <c r="EZ10" t="inlineStr"/>
-      <c r="FA10" t="inlineStr"/>
-      <c r="FB10" t="inlineStr"/>
-      <c r="FC10" t="inlineStr"/>
-      <c r="FD10" t="inlineStr"/>
-      <c r="FE10" t="inlineStr"/>
-      <c r="FF10" t="inlineStr"/>
-      <c r="FG10" t="inlineStr"/>
-      <c r="FH10" t="inlineStr"/>
-      <c r="FI10" t="inlineStr"/>
-      <c r="FJ10" t="inlineStr"/>
-      <c r="FK10" t="inlineStr"/>
-      <c r="FL10" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ9"/>
+  <dimension ref="A1:FQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CVDZV</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ZCVDV</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>RH | Side | SDVd | RH | ZXVV</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3338,299 +3338,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
-      <c r="CE9" t="inlineStr"/>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr"/>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr"/>
-      <c r="CJ9" t="inlineStr"/>
-      <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="inlineStr"/>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="inlineStr"/>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="inlineStr"/>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="inlineStr"/>
-      <c r="DJ9" t="inlineStr"/>
-      <c r="DK9" t="inlineStr"/>
-      <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr"/>
-      <c r="DP9" t="inlineStr"/>
-      <c r="DQ9" t="inlineStr"/>
-      <c r="DR9" t="inlineStr"/>
-      <c r="DS9" t="inlineStr"/>
-      <c r="DT9" t="inlineStr"/>
-      <c r="DU9" t="inlineStr"/>
-      <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="inlineStr"/>
-      <c r="DX9" t="inlineStr"/>
-      <c r="DY9" t="inlineStr"/>
-      <c r="DZ9" t="inlineStr"/>
-      <c r="EA9" t="inlineStr"/>
-      <c r="EB9" t="inlineStr"/>
-      <c r="EC9" t="inlineStr"/>
-      <c r="ED9" t="inlineStr"/>
-      <c r="EE9" t="inlineStr"/>
-      <c r="EF9" t="inlineStr"/>
-      <c r="EG9" t="inlineStr"/>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr"/>
-      <c r="EJ9" t="inlineStr"/>
-      <c r="EK9" t="inlineStr"/>
-      <c r="EL9" t="inlineStr"/>
-      <c r="EM9" t="inlineStr"/>
-      <c r="EN9" t="inlineStr"/>
-      <c r="EO9" t="inlineStr"/>
-      <c r="EP9" t="inlineStr"/>
-      <c r="EQ9" t="inlineStr"/>
-      <c r="ER9" t="inlineStr"/>
-      <c r="ES9" t="inlineStr"/>
-      <c r="ET9" t="inlineStr"/>
-      <c r="EU9" t="inlineStr"/>
-      <c r="EV9" t="inlineStr"/>
-      <c r="EW9" t="inlineStr"/>
-      <c r="EX9" t="inlineStr"/>
-      <c r="EY9" t="inlineStr"/>
-      <c r="EZ9" t="inlineStr"/>
-      <c r="FA9" t="inlineStr"/>
-      <c r="FB9" t="inlineStr"/>
-      <c r="FC9" t="inlineStr"/>
-      <c r="FD9" t="inlineStr"/>
-      <c r="FE9" t="inlineStr"/>
-      <c r="FF9" t="inlineStr"/>
-      <c r="FG9" t="inlineStr"/>
-      <c r="FH9" t="inlineStr"/>
-      <c r="FI9" t="inlineStr"/>
-      <c r="FJ9" t="inlineStr"/>
-      <c r="FK9" t="inlineStr"/>
-      <c r="FL9" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ8"/>
+  <dimension ref="A1:FQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EFGeq</t>
+          <t>RGSDG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EGWEGWE</t>
+          <t>DZSVBZDV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RH | Side | WEGWEG | RH | GSDEGAG</t>
+          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RGSDG</t>
+          <t>SAvfas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DZSVBZDV</t>
+          <t>AFsDFFWAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
+          <t>RH | Side | SFCc | RH | DVZDGV</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAvfas</t>
+          <t>VCNBVBN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AFsDFFWAS</t>
+          <t>VFBFCXB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RH | Side | SFCc | RH | DVZDGV</t>
+          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3045,299 +3045,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
-      <c r="BX8" t="inlineStr"/>
-      <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
-      <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="inlineStr"/>
-      <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="inlineStr"/>
-      <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="inlineStr"/>
-      <c r="CQ8" t="inlineStr"/>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
-      <c r="CX8" t="inlineStr"/>
-      <c r="CY8" t="inlineStr"/>
-      <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="inlineStr"/>
-      <c r="DD8" t="inlineStr"/>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="inlineStr"/>
-      <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
-      <c r="DM8" t="inlineStr"/>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr"/>
-      <c r="DP8" t="inlineStr"/>
-      <c r="DQ8" t="inlineStr"/>
-      <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
-      <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="inlineStr"/>
-      <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
-      <c r="DZ8" t="inlineStr"/>
-      <c r="EA8" t="inlineStr"/>
-      <c r="EB8" t="inlineStr"/>
-      <c r="EC8" t="inlineStr"/>
-      <c r="ED8" t="inlineStr"/>
-      <c r="EE8" t="inlineStr"/>
-      <c r="EF8" t="inlineStr"/>
-      <c r="EG8" t="inlineStr"/>
-      <c r="EH8" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr"/>
-      <c r="EJ8" t="inlineStr"/>
-      <c r="EK8" t="inlineStr"/>
-      <c r="EL8" t="inlineStr"/>
-      <c r="EM8" t="inlineStr"/>
-      <c r="EN8" t="inlineStr"/>
-      <c r="EO8" t="inlineStr"/>
-      <c r="EP8" t="inlineStr"/>
-      <c r="EQ8" t="inlineStr"/>
-      <c r="ER8" t="inlineStr"/>
-      <c r="ES8" t="inlineStr"/>
-      <c r="ET8" t="inlineStr"/>
-      <c r="EU8" t="inlineStr"/>
-      <c r="EV8" t="inlineStr"/>
-      <c r="EW8" t="inlineStr"/>
-      <c r="EX8" t="inlineStr"/>
-      <c r="EY8" t="inlineStr"/>
-      <c r="EZ8" t="inlineStr"/>
-      <c r="FA8" t="inlineStr"/>
-      <c r="FB8" t="inlineStr"/>
-      <c r="FC8" t="inlineStr"/>
-      <c r="FD8" t="inlineStr"/>
-      <c r="FE8" t="inlineStr"/>
-      <c r="FF8" t="inlineStr"/>
-      <c r="FG8" t="inlineStr"/>
-      <c r="FH8" t="inlineStr"/>
-      <c r="FI8" t="inlineStr"/>
-      <c r="FJ8" t="inlineStr"/>
-      <c r="FK8" t="inlineStr"/>
-      <c r="FL8" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ7"/>
+  <dimension ref="A1:FQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RGSDG</t>
+          <t>SAvfas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DZSVBZDV</t>
+          <t>AFsDFFWAS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RH | Side | SDVBZ | RH | SDFBZFD</t>
+          <t>RH | Side | SFCc | RH | DVZDGV</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAvfas</t>
+          <t>VCNBVBN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AFsDFFWAS</t>
+          <t>VFBFCXB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RH | Side | SFCc | RH | DVZDGV</t>
+          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2752,299 +2752,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="inlineStr"/>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
-      <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="inlineStr"/>
-      <c r="DG7" t="inlineStr"/>
-      <c r="DH7" t="inlineStr"/>
-      <c r="DI7" t="inlineStr"/>
-      <c r="DJ7" t="inlineStr"/>
-      <c r="DK7" t="inlineStr"/>
-      <c r="DL7" t="inlineStr"/>
-      <c r="DM7" t="inlineStr"/>
-      <c r="DN7" t="inlineStr"/>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
-      <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
-      <c r="DT7" t="inlineStr"/>
-      <c r="DU7" t="inlineStr"/>
-      <c r="DV7" t="inlineStr"/>
-      <c r="DW7" t="inlineStr"/>
-      <c r="DX7" t="inlineStr"/>
-      <c r="DY7" t="inlineStr"/>
-      <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="inlineStr"/>
-      <c r="EB7" t="inlineStr"/>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
-      <c r="EE7" t="inlineStr"/>
-      <c r="EF7" t="inlineStr"/>
-      <c r="EG7" t="inlineStr"/>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr"/>
-      <c r="EJ7" t="inlineStr"/>
-      <c r="EK7" t="inlineStr"/>
-      <c r="EL7" t="inlineStr"/>
-      <c r="EM7" t="inlineStr"/>
-      <c r="EN7" t="inlineStr"/>
-      <c r="EO7" t="inlineStr"/>
-      <c r="EP7" t="inlineStr"/>
-      <c r="EQ7" t="inlineStr"/>
-      <c r="ER7" t="inlineStr"/>
-      <c r="ES7" t="inlineStr"/>
-      <c r="ET7" t="inlineStr"/>
-      <c r="EU7" t="inlineStr"/>
-      <c r="EV7" t="inlineStr"/>
-      <c r="EW7" t="inlineStr"/>
-      <c r="EX7" t="inlineStr"/>
-      <c r="EY7" t="inlineStr"/>
-      <c r="EZ7" t="inlineStr"/>
-      <c r="FA7" t="inlineStr"/>
-      <c r="FB7" t="inlineStr"/>
-      <c r="FC7" t="inlineStr"/>
-      <c r="FD7" t="inlineStr"/>
-      <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr"/>
-      <c r="FG7" t="inlineStr"/>
-      <c r="FH7" t="inlineStr"/>
-      <c r="FI7" t="inlineStr"/>
-      <c r="FJ7" t="inlineStr"/>
-      <c r="FK7" t="inlineStr"/>
-      <c r="FL7" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ6"/>
+  <dimension ref="A1:FQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAvfas</t>
+          <t>VCNBVBN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AFsDFFWAS</t>
+          <t>VFBFCXB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RH | Side | SFCc | RH | DVZDGV</t>
+          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2459,299 +2459,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="inlineStr"/>
-      <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
-      <c r="DD6" t="inlineStr"/>
-      <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="inlineStr"/>
-      <c r="DG6" t="inlineStr"/>
-      <c r="DH6" t="inlineStr"/>
-      <c r="DI6" t="inlineStr"/>
-      <c r="DJ6" t="inlineStr"/>
-      <c r="DK6" t="inlineStr"/>
-      <c r="DL6" t="inlineStr"/>
-      <c r="DM6" t="inlineStr"/>
-      <c r="DN6" t="inlineStr"/>
-      <c r="DO6" t="inlineStr"/>
-      <c r="DP6" t="inlineStr"/>
-      <c r="DQ6" t="inlineStr"/>
-      <c r="DR6" t="inlineStr"/>
-      <c r="DS6" t="inlineStr"/>
-      <c r="DT6" t="inlineStr"/>
-      <c r="DU6" t="inlineStr"/>
-      <c r="DV6" t="inlineStr"/>
-      <c r="DW6" t="inlineStr"/>
-      <c r="DX6" t="inlineStr"/>
-      <c r="DY6" t="inlineStr"/>
-      <c r="DZ6" t="inlineStr"/>
-      <c r="EA6" t="inlineStr"/>
-      <c r="EB6" t="inlineStr"/>
-      <c r="EC6" t="inlineStr"/>
-      <c r="ED6" t="inlineStr"/>
-      <c r="EE6" t="inlineStr"/>
-      <c r="EF6" t="inlineStr"/>
-      <c r="EG6" t="inlineStr"/>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr"/>
-      <c r="EJ6" t="inlineStr"/>
-      <c r="EK6" t="inlineStr"/>
-      <c r="EL6" t="inlineStr"/>
-      <c r="EM6" t="inlineStr"/>
-      <c r="EN6" t="inlineStr"/>
-      <c r="EO6" t="inlineStr"/>
-      <c r="EP6" t="inlineStr"/>
-      <c r="EQ6" t="inlineStr"/>
-      <c r="ER6" t="inlineStr"/>
-      <c r="ES6" t="inlineStr"/>
-      <c r="ET6" t="inlineStr"/>
-      <c r="EU6" t="inlineStr"/>
-      <c r="EV6" t="inlineStr"/>
-      <c r="EW6" t="inlineStr"/>
-      <c r="EX6" t="inlineStr"/>
-      <c r="EY6" t="inlineStr"/>
-      <c r="EZ6" t="inlineStr"/>
-      <c r="FA6" t="inlineStr"/>
-      <c r="FB6" t="inlineStr"/>
-      <c r="FC6" t="inlineStr"/>
-      <c r="FD6" t="inlineStr"/>
-      <c r="FE6" t="inlineStr"/>
-      <c r="FF6" t="inlineStr"/>
-      <c r="FG6" t="inlineStr"/>
-      <c r="FH6" t="inlineStr"/>
-      <c r="FI6" t="inlineStr"/>
-      <c r="FJ6" t="inlineStr"/>
-      <c r="FK6" t="inlineStr"/>
-      <c r="FL6" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ5"/>
+  <dimension ref="A1:FQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VCNBVBN</t>
+          <t>sbghsdbghz</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VFBFCXB</t>
+          <t>sxDFBdzr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RH | Side | FXBNXVB | RH | XBNDFXZBHDF</t>
+          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sbghsdbghz</t>
+          <t>daGFAGD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sxDFBdzr</t>
+          <t>SDAGS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2166,299 +2166,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="inlineStr"/>
-      <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
-      <c r="DT5" t="inlineStr"/>
-      <c r="DU5" t="inlineStr"/>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
-      <c r="EB5" t="inlineStr"/>
-      <c r="EC5" t="inlineStr"/>
-      <c r="ED5" t="inlineStr"/>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
-      <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
-      <c r="EO5" t="inlineStr"/>
-      <c r="EP5" t="inlineStr"/>
-      <c r="EQ5" t="inlineStr"/>
-      <c r="ER5" t="inlineStr"/>
-      <c r="ES5" t="inlineStr"/>
-      <c r="ET5" t="inlineStr"/>
-      <c r="EU5" t="inlineStr"/>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
-      <c r="EX5" t="inlineStr"/>
-      <c r="EY5" t="inlineStr"/>
-      <c r="EZ5" t="inlineStr"/>
-      <c r="FA5" t="inlineStr"/>
-      <c r="FB5" t="inlineStr"/>
-      <c r="FC5" t="inlineStr"/>
-      <c r="FD5" t="inlineStr"/>
-      <c r="FE5" t="inlineStr"/>
-      <c r="FF5" t="inlineStr"/>
-      <c r="FG5" t="inlineStr"/>
-      <c r="FH5" t="inlineStr"/>
-      <c r="FI5" t="inlineStr"/>
-      <c r="FJ5" t="inlineStr"/>
-      <c r="FK5" t="inlineStr"/>
-      <c r="FL5" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ4"/>
+  <dimension ref="A1:FQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>daGFAGD</t>
+          <t>uiytrkiy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SDAGS</t>
+          <t>hglkclkhhl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RH | Side | sxzbdxf | RH | fndbzde</t>
+          <t>RH | Side | ytidlk | RH | tdylkdl</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1873,299 +1873,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FUSO Canter</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FE84</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>uiytrkiy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>hglkclkhhl</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>RH | Side | ytidlk | RH | tdylkdl</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Weld Shop</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
-      <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="inlineStr"/>
-      <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="inlineStr"/>
-      <c r="DM4" t="inlineStr"/>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
-      <c r="DR4" t="inlineStr"/>
-      <c r="DS4" t="inlineStr"/>
-      <c r="DT4" t="inlineStr"/>
-      <c r="DU4" t="inlineStr"/>
-      <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr"/>
-      <c r="DX4" t="inlineStr"/>
-      <c r="DY4" t="inlineStr"/>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
-      <c r="EF4" t="inlineStr"/>
-      <c r="EG4" t="inlineStr"/>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>Over Tightening</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="inlineStr"/>
-      <c r="EK4" t="inlineStr"/>
-      <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr"/>
-      <c r="EO4" t="inlineStr"/>
-      <c r="EP4" t="inlineStr"/>
-      <c r="EQ4" t="inlineStr"/>
-      <c r="ER4" t="inlineStr"/>
-      <c r="ES4" t="inlineStr"/>
-      <c r="ET4" t="inlineStr"/>
-      <c r="EU4" t="inlineStr"/>
-      <c r="EV4" t="inlineStr"/>
-      <c r="EW4" t="inlineStr"/>
-      <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="inlineStr"/>
-      <c r="EZ4" t="inlineStr"/>
-      <c r="FA4" t="inlineStr"/>
-      <c r="FB4" t="inlineStr"/>
-      <c r="FC4" t="inlineStr"/>
-      <c r="FD4" t="inlineStr"/>
-      <c r="FE4" t="inlineStr"/>
-      <c r="FF4" t="inlineStr"/>
-      <c r="FG4" t="inlineStr"/>
-      <c r="FH4" t="inlineStr"/>
-      <c r="FI4" t="inlineStr"/>
-      <c r="FJ4" t="inlineStr"/>
-      <c r="FK4" t="inlineStr"/>
-      <c r="FL4" t="inlineStr">
-        <is>
-          <t>QFL4-20261028-0001</t>
-        </is>
-      </c>
-      <c r="FM4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FN4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FO4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FP4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="FQ4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ3"/>
+  <dimension ref="A1:FQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1873,6 +1873,279 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FUSO Canter</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FE84</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ykytdk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kdjyktk</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Weld Shop</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Over Tightening</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>RH | Side | ykdt | RH | fghkcy</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Weld Shop</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>Over Tightening</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr"/>
+      <c r="FC4" t="inlineStr"/>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>QFL4-20261028-0001</t>
+        </is>
+      </c>
+      <c r="FM4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FN4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FO4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FP4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FQ4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_data.xlsx
+++ b/audit_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ4"/>
+  <dimension ref="A1:FQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,32 +1912,50 @@
           <t>Over Tightening</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1964,8 +1982,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -2146,6 +2166,279 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FUSO Canter</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FE84</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y542323</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Final Confirmation</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scratch</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>LH | Upper Side | Radiator | RH | Damage</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Final Confirmation</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>Scratch</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr"/>
+      <c r="FE5" t="inlineStr"/>
+      <c r="FF5" t="inlineStr"/>
+      <c r="FG5" t="inlineStr"/>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>QFL4-20261028-0001</t>
+        </is>
+      </c>
+      <c r="FM5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FN5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FO5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FP5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="FQ5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
